--- a/data/trans_dic/Q17F_D_R3-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Q17F_D_R3-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo de espera en días hasta la consulta en el centro sanitario, cuartil más desfavorable (Cuartil IV de 2023: &gt;15 días)</t>
+          <t>Tiempo de espera en días hasta la consulta en el centro sanitario, cuartil más desfavorable (Cuartil IV de 2023: &gt;15 días) (tasa de respuesta: 94,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,29; 17,16</t>
+          <t>9,42; 16,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,84; 17,73</t>
+          <t>9,94; 17,73</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,51; 16,81</t>
+          <t>8,84; 16,99</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,39; 23,74</t>
+          <t>12,13; 24,11</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,13; 11,02</t>
+          <t>6,23; 11,01</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,18; 11,16</t>
+          <t>6,03; 10,96</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,26; 14,8</t>
+          <t>8,51; 15,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,79; 24,19</t>
+          <t>15,41; 23,99</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,17; 12,41</t>
+          <t>8,07; 12,46</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,18; 12,32</t>
+          <t>8,22; 12,45</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8,97; 14,56</t>
+          <t>9,11; 14,52</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,69; 22,17</t>
+          <t>15,43; 22,4</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,4; 14,85</t>
+          <t>7,38; 15,33</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,76; 14,61</t>
+          <t>7,89; 14,54</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,09; 12,89</t>
+          <t>7,03; 13,09</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>13,26; 20,7</t>
+          <t>12,89; 20,65</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>9,78; 17,16</t>
+          <t>10,0; 17,2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,01; 16,36</t>
+          <t>10,14; 16,0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,73; 16,69</t>
+          <t>10,78; 16,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,29; 22,7</t>
+          <t>11,19; 23,29</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,87; 15,27</t>
+          <t>9,73; 15,54</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10,0; 14,49</t>
+          <t>9,88; 14,5</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,9; 14,22</t>
+          <t>9,88; 13,98</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,54; 21,0</t>
+          <t>13,15; 20,61</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,46; 27,6</t>
+          <t>7,73; 28,22</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,8; 29,46</t>
+          <t>8,7; 28,76</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,54; 20,47</t>
+          <t>6,59; 20,4</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,66; 32,88</t>
+          <t>16,62; 32,05</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,66; 20,55</t>
+          <t>7,44; 19,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,84; 19,09</t>
+          <t>6,02; 18,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,23; 19,87</t>
+          <t>7,13; 19,93</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,52; 21,07</t>
+          <t>11,62; 21,7</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,74; 20,15</t>
+          <t>8,75; 19,89</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,12; 18,96</t>
+          <t>8,46; 19,94</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,3; 17,79</t>
+          <t>8,26; 17,17</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,52; 24,38</t>
+          <t>15,0; 24,5</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,8; 14,89</t>
+          <t>9,76; 15,03</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,16; 15,14</t>
+          <t>10,09; 15,04</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,51; 13,03</t>
+          <t>8,97; 13,56</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,2; 21,52</t>
+          <t>15,02; 21,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,83; 12,79</t>
+          <t>8,64; 12,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,69; 12,5</t>
+          <t>8,72; 12,55</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,54; 14,8</t>
+          <t>10,56; 14,63</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,77; 21,5</t>
+          <t>13,66; 21,26</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,76; 12,96</t>
+          <t>9,77; 12,94</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,83; 12,81</t>
+          <t>9,84; 12,9</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,4; 13,54</t>
+          <t>10,38; 13,41</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,35; 20,38</t>
+          <t>15,48; 20,52</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Tiempo de espera en días hasta la consulta en el centro sanitario, cuartil más desfavorable (Cuartil IV de 2023: &gt;15 días)</t>
+          <t>Tiempo de espera en días hasta la consulta en el centro sanitario, cuartil más desfavorable (Cuartil IV de 2023: &gt;15 días) (tasa de respuesta: 94,47%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>27807; 51394</t>
+          <t>28218; 50455</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32192; 57983</t>
+          <t>32513; 57999</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21020; 41519</t>
+          <t>21829; 41942</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15976; 30620</t>
+          <t>15650; 31106</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30174; 54246</t>
+          <t>30675; 54211</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>32610; 58838</t>
+          <t>31821; 57796</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>33322; 59694</t>
+          <t>34300; 61378</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>34613; 53049</t>
+          <t>33795; 52602</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>64694; 98217</t>
+          <t>63918; 98627</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>69903; 105277</t>
+          <t>70240; 106393</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58292; 94681</t>
+          <t>59220; 94391</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>54641; 77224</t>
+          <t>53744; 77995</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17496; 35098</t>
+          <t>17433; 36239</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>26631; 50107</t>
+          <t>27081; 49897</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31852; 57936</t>
+          <t>31598; 58830</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46752; 73012</t>
+          <t>45438; 72811</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>35882; 62960</t>
+          <t>36687; 63093</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>47522; 77694</t>
+          <t>48175; 75977</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60664; 94359</t>
+          <t>60955; 95186</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>54436; 109464</t>
+          <t>53971; 112293</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>59527; 92090</t>
+          <t>58673; 93754</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>81831; 118543</t>
+          <t>80843; 118601</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>100446; 144239</t>
+          <t>100246; 141868</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>113015; 175346</t>
+          <t>109826; 172104</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5166; 19112</t>
+          <t>5351; 19538</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6580; 22035</t>
+          <t>6505; 21511</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7499; 23481</t>
+          <t>7560; 23411</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20662; 40781</t>
+          <t>20610; 39757</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8361; 22437</t>
+          <t>8123; 21517</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6122; 19999</t>
+          <t>6310; 19093</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9522; 26178</t>
+          <t>9386; 26258</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17037; 31171</t>
+          <t>17184; 32092</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15592; 35949</t>
+          <t>15614; 35491</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>14585; 34036</t>
+          <t>15199; 35806</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20455; 43851</t>
+          <t>20357; 42315</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>42204; 66295</t>
+          <t>40794; 66635</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59288; 90084</t>
+          <t>59039; 90940</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>75724; 112754</t>
+          <t>75129; 112036</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>68982; 105671</t>
+          <t>72712; 109975</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>92069; 130341</t>
+          <t>90994; 130505</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>85481; 123824</t>
+          <t>83660; 124655</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>96227; 138335</t>
+          <t>96483; 138917</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>115919; 162795</t>
+          <t>116166; 160977</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>116931; 182598</t>
+          <t>116052; 180560</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>153636; 203874</t>
+          <t>153644; 203563</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182085; 237221</t>
+          <t>182171; 238829</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>198685; 258719</t>
+          <t>198345; 256271</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>223360; 296625</t>
+          <t>225253; 298623</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/Q17F_D_R3-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/Q17F_D_R3-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,27 +684,27 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>20,61%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>10,02%</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>10,21%</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>11,73%</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
           <t>19,66%</t>
-        </is>
-      </c>
-      <c r="K4" s="2" t="inlineStr">
-        <is>
-          <t>10,02%</t>
-        </is>
-      </c>
-      <c r="L4" s="2" t="inlineStr">
-        <is>
-          <t>10,21%</t>
-        </is>
-      </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>11,73%</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
-        <is>
-          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>9,42; 16,85</t>
+          <t>9,58; 16,6</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>9,94; 17,73</t>
+          <t>9,88; 17,95</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8,84; 16,99</t>
+          <t>8,69; 17,03</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,13; 24,11</t>
+          <t>12,37; 24,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,23; 11,01</t>
+          <t>6,16; 10,9</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>6,03; 10,96</t>
+          <t>6,02; 11,05</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>8,51; 15,22</t>
+          <t>8,36; 14,84</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>15,41; 23,99</t>
+          <t>16,67; 25,04</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>8,07; 12,46</t>
+          <t>8,16; 12,42</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>8,22; 12,45</t>
+          <t>8,28; 12,75</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9,11; 14,52</t>
+          <t>9,12; 14,43</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,43; 22,4</t>
+          <t>16,33; 23,55</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>16,66%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>19,31%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>7,38; 15,33</t>
+          <t>7,43; 15,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>7,89; 14,54</t>
+          <t>7,9; 14,7</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7,03; 13,09</t>
+          <t>7,28; 13,52</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12,89; 20,65</t>
+          <t>12,86; 20,49</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,0; 17,2</t>
+          <t>9,8; 17,52</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,14; 16,0</t>
+          <t>10,2; 16,53</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>10,78; 16,84</t>
+          <t>10,81; 16,84</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>11,19; 23,29</t>
+          <t>18,07; 25,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,73; 15,54</t>
+          <t>9,86; 15,31</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>9,88; 14,5</t>
+          <t>9,8; 14,45</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>9,88; 13,98</t>
+          <t>9,93; 14,18</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>13,15; 20,61</t>
+          <t>16,83; 22,08</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>23,61%</t>
+          <t>23,87%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,56%</t>
+          <t>20,13%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>7,73; 28,22</t>
+          <t>7,24; 28,02</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>8,7; 28,76</t>
+          <t>7,74; 28,01</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>6,59; 20,4</t>
+          <t>6,35; 19,41</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>16,62; 32,05</t>
+          <t>17,04; 31,94</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>7,44; 19,71</t>
+          <t>6,97; 20,44</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,02; 18,23</t>
+          <t>5,35; 18,29</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>7,13; 19,93</t>
+          <t>6,9; 20,65</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>11,62; 21,7</t>
+          <t>12,38; 22,53</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>8,75; 19,89</t>
+          <t>8,51; 19,56</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8,46; 19,94</t>
+          <t>8,82; 19,44</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>8,26; 17,17</t>
+          <t>8,43; 18,09</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>15,0; 24,5</t>
+          <t>15,61; 24,95</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,45%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>20,39%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>18,31%</t>
+          <t>19,56%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>9,76; 15,03</t>
+          <t>9,69; 15,14</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>10,09; 15,04</t>
+          <t>10,14; 15,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>8,97; 13,56</t>
+          <t>8,71; 13,33</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>15,02; 21,55</t>
+          <t>15,67; 21,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>8,64; 12,87</t>
+          <t>8,75; 12,85</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>8,72; 12,55</t>
+          <t>8,76; 12,44</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,56; 14,63</t>
+          <t>10,53; 15,01</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>13,66; 21,26</t>
+          <t>18,13; 22,76</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9,77; 12,94</t>
+          <t>9,88; 13,09</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>9,84; 12,9</t>
+          <t>9,89; 12,99</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>10,38; 13,41</t>
+          <t>10,37; 13,42</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>15,48; 20,52</t>
+          <t>17,7; 21,56</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>22353</t>
+          <t>24692</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>43105</t>
+          <t>48781</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>65458</t>
+          <t>73473</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>28218; 50455</t>
+          <t>28692; 49707</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>32513; 57999</t>
+          <t>32313; 58696</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>21829; 41942</t>
+          <t>21462; 42040</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>15650; 31106</t>
+          <t>16944; 33538</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>30675; 54211</t>
+          <t>30309; 53645</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>31821; 57796</t>
+          <t>31776; 58297</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>34300; 61378</t>
+          <t>33707; 59849</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>33795; 52602</t>
+          <t>39455; 59280</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>63918; 98627</t>
+          <t>64571; 98339</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>70240; 106393</t>
+          <t>70783; 108962</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>59220; 94391</t>
+          <t>59305; 93806</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>53744; 77995</t>
+          <t>61021; 88026</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>58310</t>
+          <t>63023</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>89429</t>
+          <t>100243</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>147739</t>
+          <t>163267</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>17433; 36239</t>
+          <t>17562; 36680</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>27081; 49897</t>
+          <t>27100; 50435</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>31598; 58830</t>
+          <t>32726; 60744</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>45438; 72811</t>
+          <t>48656; 77497</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>36687; 63093</t>
+          <t>35945; 64264</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>48175; 75977</t>
+          <t>48431; 78482</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>60955; 95186</t>
+          <t>61112; 95214</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>53971; 112293</t>
+          <t>84412; 117802</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>58673; 93754</t>
+          <t>59482; 92343</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>80843; 118601</t>
+          <t>80162; 118170</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>100246; 141868</t>
+          <t>100782; 143894</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>109826; 172104</t>
+          <t>142324; 186660</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>29287</t>
+          <t>32383</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>23921</t>
+          <t>28534</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>53208</t>
+          <t>60917</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>5351; 19538</t>
+          <t>5016; 19398</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6505; 21511</t>
+          <t>5786; 20954</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7560; 23411</t>
+          <t>7283; 22274</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>20610; 39757</t>
+          <t>23122; 43323</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>8123; 21517</t>
+          <t>7610; 22321</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>6310; 19093</t>
+          <t>5609; 19159</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9386; 26258</t>
+          <t>9086; 27197</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>17184; 32092</t>
+          <t>20669; 37617</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>15614; 35491</t>
+          <t>15186; 34900</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>15199; 35806</t>
+          <t>15845; 34912</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20357; 42315</t>
+          <t>20780; 44578</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>40794; 66635</t>
+          <t>47245; 75506</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>109950</t>
+          <t>120098</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>156456</t>
+          <t>177559</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>266406</t>
+          <t>297657</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>59039; 90940</t>
+          <t>58656; 91638</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>75129; 112036</t>
+          <t>75536; 113549</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>72712; 109975</t>
+          <t>70666; 108092</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>90994; 130505</t>
+          <t>101987; 140897</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>83660; 124655</t>
+          <t>84711; 124464</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>96483; 138917</t>
+          <t>97008; 137722</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>116166; 160977</t>
+          <t>115862; 165171</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>116052; 180560</t>
+          <t>157889; 198228</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>153644; 203563</t>
+          <t>155508; 205889</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>182171; 238829</t>
+          <t>183213; 240491</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>198345; 256271</t>
+          <t>198114; 256499</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>225253; 298623</t>
+          <t>269367; 328039</t>
         </is>
       </c>
     </row>
